--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8580BDDF-7229-45B6-B833-152A1ABBD6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F121F-2943-4E8F-A785-EBEDDC7EE891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -103,6 +103,9 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
+    <t>ItemTable</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
@@ -124,46 +127,41 @@
     <t>item</t>
   </si>
   <si>
-    <t>ItemTable</t>
-  </si>
-  <si>
     <t>LotteryTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Lottery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>lottery.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽奖池配置</t>
   </si>
   <si>
     <t>lottery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>抽奖池配置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>map</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HomeTable</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>home.xlsx</t>
+  </si>
+  <si>
+    <t>家具配置</t>
+  </si>
+  <si>
+    <t>home</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,32 +170,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -209,25 +193,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -500,172 +477,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
-    <col min="11" max="11" width="7.5546875" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>38</v>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F121F-2943-4E8F-A785-EBEDDC7EE891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2DA4AB-2AB5-4C96-8EC9-808A08556755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5448" yWindow="2748" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -155,13 +155,77 @@
   </si>
   <si>
     <t>home</t>
+  </si>
+  <si>
+    <t>MissionTable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mission.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseTable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>base.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础属性配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +236,15 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,8 +271,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -477,10 +553,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -658,6 +735,64 @@
       </c>
       <c r="K6" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FEEAA3-3DBB-45EE-B688-E95CFC2468D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7680BBB-9C67-42AE-BE67-1B2C180E5D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31056" yWindow="-5616" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -215,6 +215,38 @@
   </si>
   <si>
     <t>缩放配置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConvenienceTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Convenience</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>convenience.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>map</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>便利店配置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>convenience</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -267,7 +299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -275,6 +307,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -550,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="2" customWidth="1"/>
@@ -850,6 +883,35 @@
         <v>63</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MiniTemplate/Datas/__tables__.xlsx
+++ b/MiniTemplate/Datas/__tables__.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="22" customWidth="1" style="2" min="1" max="1"/>
@@ -832,7 +832,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>WorkTable</t>
         </is>
@@ -922,47 +922,92 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>BuffConfigTable</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>BuffConfig</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>buffConfig.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>BUFF ??</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>buffConfig</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>GrowTable</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Grow</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>grow.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>时光藏馆成长配置</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>grow</t>
         </is>
       </c>
     </row>
